--- a/artfynd/A 39763-2022 artfynd.xlsx
+++ b/artfynd/A 39763-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 39763-2022 artfynd.xlsx
+++ b/artfynd/A 39763-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,19 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>56442822</v>
+        <v>56442461</v>
       </c>
       <c r="B2" t="n">
-        <v>88896</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91375</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>679392.2831038185</v>
+        <v>679676</v>
       </c>
       <c r="R2" t="n">
-        <v>6670046.773148973</v>
+        <v>6670230</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,24 +743,14 @@
           <t>2004-08-08</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2004-08-08</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>En halv häxring, 2 m i diameter, under äldre gran och tall.</t>
+          <t>1 m lång sträng under äldre gran och tall.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,59 +782,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>69524577</v>
+        <v>56442822</v>
       </c>
       <c r="B3" t="n">
-        <v>90645</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91375</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4361</v>
+        <v>720</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Violgubbe</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Gomphus clavatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Pers.) Gray</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Fridhem 5 km SSO om Gimo, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>679402.4395834452</v>
+        <v>679392</v>
       </c>
       <c r="R3" t="n">
-        <v>6670053.758188771</v>
+        <v>6670047</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,24 +850,14 @@
           <t>2004-08-08</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2004-08-08</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ca. 50 ex.</t>
+          <t>En halv häxring, 2 m i diameter, under äldre gran och tall.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -928,15 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>69562568</v>
+        <v>69524577</v>
       </c>
       <c r="B4" t="n">
-        <v>88937</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -944,26 +900,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>256756</v>
+        <v>4361</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blek fingersvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ramaria pallida</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schaeff.) Ricken</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -977,10 +933,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>679392.5267180069</v>
+        <v>679402</v>
       </c>
       <c r="R4" t="n">
-        <v>6670041.794233089</v>
+        <v>6670054</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1010,24 +966,14 @@
           <t>2004-08-08</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2004-08-08</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>1 ex. under äldre granar.</t>
+          <t>Ca. 50 ex.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1062,16 +1008,11 @@
         <v>75945729</v>
       </c>
       <c r="B5" t="n">
-        <v>90674</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1084,12 +1025,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1108,10 +1049,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>679506.655344485</v>
+        <v>679507</v>
       </c>
       <c r="R5" t="n">
-        <v>6670110.26439691</v>
+        <v>6670110</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1141,19 +1082,9 @@
           <t>2004-08-08</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2004-08-08</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1194,12 +1125,7 @@
         <v>76009476</v>
       </c>
       <c r="B6" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1245,10 +1171,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>679431.9243396943</v>
+        <v>679432</v>
       </c>
       <c r="R6" t="n">
-        <v>6670064.184535605</v>
+        <v>6670064</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1278,19 +1204,9 @@
           <t>2004-08-08</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2004-08-08</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1319,6 +1235,238 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>69562567</v>
+      </c>
+      <c r="B7" t="n">
+        <v>91428</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>256756</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Blek fingersvamp</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Ramaria pallida</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Ricken</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Fridhem 5 km SSO om Gimo, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>679591</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6670181</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Hökhuvud</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2004-08-08</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2004-08-08</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>8 ex. under äldre granar.</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Äldre, örtrik barrskog.</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>69562568</v>
+      </c>
+      <c r="B8" t="n">
+        <v>91428</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>256756</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Blek fingersvamp</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Ramaria pallida</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Ricken</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Fridhem 5 km SSO om Gimo, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>679393</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6670042</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Hökhuvud</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2004-08-08</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2004-08-08</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>1 ex. under äldre granar.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Äldre, örtrik barrskog.</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 39763-2022 artfynd.xlsx
+++ b/artfynd/A 39763-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56442461</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56442822</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1002,6 +1017,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69524577</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1119,6 +1139,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75945729</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1235,6 +1260,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76009476</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1351,6 +1381,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69562567</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1467,8 +1502,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69562568</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>